--- a/docs/V2.1开发计划_领导版.xlsx
+++ b/docs/V2.1开发计划_领导版.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V2.1开发计划" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能模块详细说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部门职责与权限矩阵" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10周甘特图" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -97,12 +97,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4F9FC"/>
+        <fgColor rgb="00F0F7FC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -118,11 +123,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF3E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -730,12 +730,12 @@
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="54" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>序号</t>
@@ -743,7 +743,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>分类</t>
+          <t>负责部门</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="96" customHeight="1">
+    <row r="2" ht="102" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -789,26 +789,26 @@
       <c r="E2" s="5" t="inlineStr">
         <is>
           <t>• 部门数据模型：新增 department 表，User/Quotation/Material 加 department_id 字段
-• 用户管理：部门归属、跨部门标记（is_cross_dept），admin 全局用户不受限制
+• 用户管理：部门归属、跨部门标记（is_cross_dept），admin 全局用户不受部门限制
 • 角色权限体系重构：角色表支持「部门级管理员」，权限粒度精细化（view/create/edit/delete/approve）
 • 权限中间件：所有 API 自动加 department_id 过滤，普通用户仅访问本部门数据
-• 操作日志：记录所有关键操作（谁/何时/对什么/做了什么）
+• 操作日志：记录所有关键操作（谁/何时/对什么/做了什么），支持按模块/操作类型筛选
 • 数据迁移：现有报价单/用户/物料批量回填 department_id</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>基础数据模型，是所有功能的前提条件，需优先完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="96" customHeight="1">
+          <t>基础数据模型，是所有部门功能的前提条件，需优先完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="102" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>机构部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -823,27 +823,28 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>• 机构信息管理：机构名称、地址、银行账户、纳税人识别号
-• 机构联系人管理：支持多联系人录入（姓名/职务/电话/邮箱）
-• 机构专属字段：质保期、结算方式、发票类型
-• 机构数据隔离：机构部用户只能操作本机构数据，view/create/edit/delete 权限独立控制
-• 机构费用项：机构专属费用类型（调试费/培训费/证书费），默认利润率配置
-• 机构报价历史：按机构统计历史报价单数量、总金额、成交率</t>
+          <t>• 税率配置：设置默认税率（0/3/6/13/17%），支持按客户/项目差异化配置
+• 物料分类系数：配置大件/普通件/其他件 分类系数，报价计算时自动应用
+• 人力费用单价：按工种（电控设计/软件开发/现场调试/装配）配置每小时单价（元/小时）
+• 运输费用单价：配置每次运输单元的单价（元/次），含国内/国外不同报价
+• 机票+签证费用单价：配置单人机票价（元/张）和单人签证费（元/人）
+• 报价有效期配置：设置默认报价有效期天数，超期自动提醒
+• 费用参数历史：记录费用单价变更历史，版本可追溯</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>机构信息是报价单的关联基础，质保/结算/发票字段影响最终报价</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="96" customHeight="1">
+          <t>销售部配置完成后，机构/电控/项目部在填写报价单时自动引用最新单价</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="102" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>电控软件部</t>
+          <t>机构部</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -853,32 +854,32 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>第2周 周三~周五</t>
+          <t>第2周 周三~第3周 周二</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>• 电控/软件模块管理：模块名称、工种类型（电控设计/软件开发/现场调试）
-• 电控负责人配置：Module → technician_lead_id，支持多技术负责人
-• 电控/软件费用项：电控设计费、PLC编程费、组态软件费、现场调试费
-• 软件人员工时记录：按工种记录工时（design/assembly/debugging），关联工时单价
-• 权限控制：电控软件部用户只能编辑本部门负责的模块内容
-• BOM清单维护：电控/软件物料清单，支持从原材料库选择或自定义录入</t>
+          <t>• 机构模块划分：根据产品类型，将报价单划分为多个机构模块（结构设计/钣金件/标准件/外购件等）
+• 机构 BOM 清单：从原材料库选择物料，填入各机构模块，支持批量添加
+• 机构专属物料：可录入仅本机构使用的私有物料（ department_id 隔离）
+• 模块参与人：设置业务负责人（business_lead）和查看者（viewer）
+• 机构费用项：模块级其他费用（调试费/培训费/证书费等），支持内部/外部不同计价
+• 机构模块权限：机构部用户只能编辑本部门的模块内容，view 权限按参与人分配</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>电控软件模块是报价单的核心组成部分，与工时成本联动</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="96" customHeight="1">
+          <t>机构部负责机械/结构类模块，是报价单物料的主要来源，需与电控软件部协同</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="102" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>项目部</t>
+          <t>电控软件部</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -888,32 +889,32 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>第3周 周一~周三</t>
+          <t>第2周 周三~第3周 周二</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>• 项目信息管理：项目名称、项目类型（线体/项目/备件）、项目经理
-• 项目关联报价单：quotation.project_id，支持一个项目关联多个报价单
-• 项目成员权限：项目成员 view/edit 项目下所有报价单，非成员 view（需申请协作）
-• 项目进度管理：阶段划分（方案设计/采购/生产/调试/验收），进度百分比
-• 参与人权限矩阵：business_lead（业务）/ technician_lead（技术）/ engineering_lead（工程）/ viewer（查看）
-• 项目文档上传：支持上传技术方案、图纸、规格书（文件管理）</t>
+          <t>• 电控模块划分：根据产品类型，将报价单划分为多个电控/软件模块（PLC控制/变频器/触摸屏/软件组态等）
+• 电控 BOM 清单：从原材料库选择物料，填入各电控模块，支持批量添加
+• 电控专属物料：可录入仅本电控部使用的私有物料（ department_id 隔离）
+• 电控工种配置：配置电控设计/软件开发/现场调试各工种的小时费率
+• 电控费用项：模块级其他费用（电控设计费/PLC编程费/现场调试费等），支持内部/外部不同计价
+• 电控模块权限：电控软件部用户只能编辑本部门的模块内容</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>参与人权限矩阵决定谁可以填写/查看/审批报价单的哪些部分</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="96" customHeight="1">
+          <t>电控软件部与机构部并行工作，各自维护本部门的模块和 BOM，共同构成完整报价单</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="102" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>销售部</t>
+          <t>项目部</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -923,26 +924,26 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>第3周 周四~第4周 周二</t>
+          <t>第3周 周三~第4周 周二</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>• 销售报价发起：销售发起新建报价单，自动带销售部门标记，流转到其他部门填写
-• 客户信息管理：客户名称、行业、联系人、意向产品、意向金额
-• 销售价格策略：折扣率（全局/客户级）、付款方式（预付/月结/阶段付）、报价有效期
-• 销售数据隔离：销售部用户只能查看/操作本销售负责的报价单
-• 销售统计面板：按销售负责人统计报价单数量、总额、成交率、丢单原因分析
-• 竞争对手信息：记录历史竞争对手报价，用于价格策略参考</t>
+          <t>• 工时记录：按工种（电控设计/软件开发/装配/调试/安装）录入工时数量（小时），自动关联人力费用单价
+• 工时内容：记录每条工时的具体工作内容，便于追溯和审计
+• 工时审批：项目负责人审批工时记录，确认后自动写入报价单 OtherFee（人力费用）
+• 运输单元配置：填写本次报价需要的运输次数（每次的运费单价由销售部配置）
+• 差旅人次配置：填写本次报价需要的机票数量和签证人数（单人单价由销售部配置）
+• 参与人权限：项目成员 view/edit 本项目报价单的工时/运输/差旅部分</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>销售是报价单的发起端，负责最终汇总和客户沟通</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="96" customHeight="1">
+          <t>项目部填写的内容（工时×单价 + 运输次数 + 差旅人次）构成报价单的主要非物料成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="102" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -966,19 +967,18 @@
           <t>• 原材料库维护：CRUD，支持分类（大件/普通件/其他件）、供应商、规格型号
 • 物料批量导入：Excel 批量导入（openpyxl），先预览后确认入库；按 code 精确匹配更新
 • 导入错误报告：返回错误行号+原因（品名为空/单价格式错误/分类不存在等）
-• 物料分类系数：大件系数/普通件系数/其他件系数，金额计算时自动应用
 • 物料部门归属：部门私有物料（仅本部门可见）vs 全局物料（所有部门可见）
 • 物料筛选：按分类/供应商/编码/品名多条件搜索，支持扫码枪快速定位
-• 物料使用历史：某物料被哪些报价单/项目使用过，便于成本参考</t>
+• 物料使用历史：某物料被哪些报价单/项目使用过，便于成本参考和复用</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>物料是报价单的核心原材料，批量导入是高频操作，需重点打磨</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="96" customHeight="1">
+          <t>原材料库是机构部和电控软件部共用的物料来源，需支持部门私有和全局物料两种模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="102" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -999,22 +999,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>• 报价单完整流程串联：销售发起 → 各部门填写 → 汇总金额 → 提交审批 → 审批通过 → 归档
-• 金额计算引擎重构：含税（含系数调整）/ 含利润 / 含人力成本，联动实时计算
+          <t>• 报价单完整流程串联：销售配置参数 → 机构/电控划分模块+填 BOM → 项目填工时/运输/差旅 → 汇总审批 → 归档
+• 金额计算引擎重构：（物料小计×分类系数 + 人力费用 + 运输费用 + 差旅费用）×（1+税率）
+• 费用自动汇总：各模块 BOM 费用 + 工时费用（工时数×单价）+ 运输（次数×单价）+ 差旅（人次×单价）
 • 版本快照增强：每次保存/提交/审批自动生成快照，存储完整报价结构 JSON
 • 版本对比 API：GET /versions/&lt;id&gt;/compare?v1=X&amp;v2=Y，返回物料/费用/金额字段级差异
 • 版本对比前端页：左右分栏展示，高亮差异字段（绿色=新增/红色=删除/橙色=修改）
-• 多格式导出：PDF（已有）/ Word（python-docx，含水印、版本号、审核状态）/ Excel（openpyxl，多Sheet）
-• 报表导出：按筛选条件导出 Excel/CSV，支持自定义列</t>
+• 多格式导出：PDF（已有）/ Word（python-docx，含水印、版本号）/ Excel（openpyxl，多Sheet：封面+物料+费用汇总）</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>整合是整个系统的最终验收，各模块联调确保数据流正确</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="96" customHeight="1">
+          <t>整合测试：销售参数是否正确引用、机构/电控 BOM 是否正确汇总、项目费用是否正确联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="102" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -1035,13 +1035,13 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>• 功能测试：报价单完整生命周期全覆盖（创建→填写→提交→审批→归档）
-• 权限测试：跨部门数据隔离 / 角色权限矩阵 / admin 全局权限
+          <t>• 功能测试：报价单完整生命周期（创建→各部门填写→汇总→审批→归档）
+• 权限测试：跨部门数据隔离 / 角色权限矩阵 / admin 全局权限 / 参与人权限
+• 费用联动测试：修改工时数量→报价单汇总金额自动更新；修改税率→税额自动重算
 • 性能测试：100+ 物料报价单加载 &lt; 2秒 / 批量导入 500 行 &lt; 10 秒
 • 数据库索引优化：quotations.department_id / modules.quotation_id / operation_logs.created_at
 • 回归测试：全量 API Postman 批量用例，核心路径 100% 通过
-• Bug 修复 + 细节打磨：按钮状态统一 / 错误提示 / 表单校验 / 空状态页面
-• 备份恢复验证：pg_dump 全量备份 + 模拟数据恢复测试
+• Bug 修复 + 细节打磨：按钮状态 / 错误提示 / 表单校验 / 空状态页面
 • Docker Swarm 重新构建镜像 + 生产环境部署 + 冒烟测试</t>
         </is>
       </c>
@@ -1062,10 +1062,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B1" s="14" t="inlineStr">
         <is>
-          <t>功能模块</t>
+          <t>职责模块</t>
         </is>
       </c>
       <c r="C1" s="14" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>创建/编辑/冻结用户，分配部门，设置跨部门权限标记</t>
+          <t>创建/编辑/冻结用户，分配部门，设置跨部门权限标记（is_cross_dept）</t>
         </is>
       </c>
     </row>
@@ -1167,589 +1167,699 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
+          <t>权限中间件</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>create/edit/delete</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>API 层面自动过滤 department_id，普通用户仅访问本部门数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>系统管理</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
           <t>操作日志</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>view</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>查看所有用户的关键操作记录（谁在何时对什么做了什么）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>机构部</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>机构信息</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>view/create/edit/delete</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>管理机构基本信息：名称/地址/银行账户/纳税人识别号/结算方式</t>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>查看所有用户的关键操作记录（谁/何时/对什么/做了什么）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>机构部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>机构联系人</t>
+          <t>税率配置</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>view/create/edit/delete</t>
+          <t>view/edit</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>管理多联系人，录入职务/电话/邮箱</t>
+          <t>设置默认税率（0/3/6/13/17%），支持按客户/项目差异化配置，版本可追溯</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>机构部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>机构费用项</t>
+          <t>物料分类系数</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>view/create/edit</t>
+          <t>view/edit</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>配置机构专属费用类型（调试费/培训费/证书费）及默认利润率</t>
+          <t>配置大件/普通件/其他件 分类系数，报价计算时自动应用</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>机构部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>机构报价历史</t>
+          <t>人力费用单价</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>view</t>
+          <t>view/edit</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>按机构维度统计历史报价单数量、总金额、成交率</t>
+          <t>按工种（电控设计/软件开发/装配/调试/安装）配置每小时单价（元/小时），内部/外部分开</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>电控软件部</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>电控模块</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>view/create/edit/delete</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>管理电控/软件模块，配置技术负责人，支持多负责人</t>
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>运输费用单价</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>view/edit</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>配置每次运输单元的单价（元/次），含国内/国外不同报价标准</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>电控软件部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>BOM清单</t>
+          <t>机票+签证单价</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>view/create/edit/delete</t>
+          <t>view/edit</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>电控/软件物料清单，从原材料库选择或自定义录入物料项</t>
+          <t>配置单人机票价（元/张）和单人签证费（元/人），含国内/国外不同报价标准</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>电控软件部</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>电控费用项</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>view/create/edit</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>电控设计费/PLC编程费/组态软件费/现场调试费配置</t>
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>报价有效期配置</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>view/edit</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>设置默认报价有效期天数，超期自动提醒</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>电控软件部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>工时记录</t>
+          <t>销售统计</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>view/create/edit/delete</t>
+          <t>view</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>按工种（design/assembly/debugging）录入工时，关联工时单价</t>
+          <t>按销售负责人统计报价单数量、总额、成交率、丢单原因分析</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>项目部</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>项目信息</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>view/create/edit/delete</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>管理项目基本信息，关联报价单，支持一个项目多个报价单</t>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>销售部</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>报价单发起</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>create/submit</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>发起新报价单，自动带销售部门标记，追踪报价单全流程状态</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>项目部</t>
+          <t>机构部</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>项目成员权限</t>
+          <t>机构模块划分</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>view/create/edit</t>
+          <t>create/edit/delete</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>添加/移除项目成员，设置成员 view/edit 权限</t>
+          <t>将报价单划分为多个机构模块（结构设计/钣金件/标准件/外购件），拖拽排序</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>项目部</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>项目进度</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>view/edit</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>维护项目阶段进度（方案/采购/生产/调试/验收）及完成百分比</t>
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>机构部</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>机构 BOM 清单</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>view/create/edit/delete</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>从原材料库选择物料填入各机构模块，支持批量添加/删除/编辑数量</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>项目部</t>
+          <t>机构部</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>项目文档</t>
+          <t>机构专属物料</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>upload/delete</t>
+          <t>view/create/edit/delete</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>上传技术方案/图纸/规格书，支持文件预览</t>
+          <t>录入仅本机构使用的私有物料，department_id 隔离，其他部门不可见</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>销售部</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>客户管理</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>view/create/edit/delete</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>管理客户信息：名称/行业/联系人/意向产品/意向金额</t>
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>机构部</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>模块参与人</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>view/create/edit</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>设置模块业务负责人（business_lead）和查看者（viewer）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>销售部</t>
+          <t>机构部</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>销售报价发起</t>
+          <t>机构费用项</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>create/submit</t>
+          <t>view/create/edit/delete</t>
         </is>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>发起新报价单，自动带销售部门标记，追踪报价单状态</t>
+          <t>模块级其他费用（调试费/培训费/证书费等），支持内部/外部不同计价</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>销售部</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>价格策略</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>view/create/edit</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>配置折扣率（全局/客户级）、付款方式、报价有效期</t>
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>电控软件部</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>电控模块划分</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>create/edit/delete</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>将报价单划分为多个电控/软件模块（PLC控制/变频器/触摸屏/软件组态），拖拽排序</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>销售部</t>
+          <t>电控软件部</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>销售统计</t>
+          <t>电控 BOM 清单</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>view</t>
+          <t>view/create/edit/delete</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>按销售负责人统计：报价单数量/总额/成交率/丢单原因</t>
+          <t>从原材料库选择物料填入各电控模块，支持批量添加/删除/编辑数量</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
-        <is>
-          <t>物料清单</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>原材料库</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>电控软件部</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>电控专属物料</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>CRUD物料：品名/编码/规格/分类/供应商/单价，部门归属设置</t>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>录入仅本电控部使用的私有物料，department_id 隔离，其他部门不可见</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>物料清单</t>
+          <t>电控软件部</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>批量导入</t>
+          <t>电控费用项</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>import/preview/confirm</t>
+          <t>view/create/edit/delete</t>
         </is>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Excel批量导入，预览确认后入库，按code精确匹配更新</t>
+          <t>模块级其他费用（电控设计费/PLC编程费/现场调试费），支持内部/外部不同计价</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>物料清单</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>分类系数</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>view/edit</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>配置大件/普通件/其他件系数，报价计算时自动应用</t>
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>项目部</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>工时记录</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>view/create/edit/delete</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>按工种录入工时数量（小时）和工作内容，关联人力费用单价，自动计算成本</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>物料清单</t>
+          <t>项目部</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>物料筛选</t>
+          <t>工时审批</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>view</t>
+          <t>approve/reject</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>多条件搜索（分类/供应商/编码/品名），支持扫码枪快速定位</t>
+          <t>项目负责人审批工时记录，确认后自动写入报价单 OtherFee（人力费用）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>物料清单</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>使用历史</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>view</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>查看物料被哪些报价单/项目使用过，便于成本参考和复用</t>
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>项目部</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>运输单元</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>view/create/edit/delete</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>填写本次报价需要的运输次数，关联销售部配置的单价，自动计算运输费用</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>项目部</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>版本快照</t>
+          <t>差旅人次</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>view/create</t>
+          <t>view/create/edit/delete</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>每次保存/提交/审批自动生成快照，可追溯历史版本</t>
+          <t>填写本次报价需要的机票数量和签证人数，关联销售部配置的单价，自动计算差旅费用</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
-        <is>
-          <t>全局</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
-        <is>
-          <t>版本对比</t>
-        </is>
-      </c>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>view</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>对比任意两个版本，字段级差异高亮展示</t>
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>项目部</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>项目进度</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>view/edit</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>维护项目阶段进度（方案/采购/生产/调试/验收），进度百分比展示</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>全局</t>
+          <t>物料清单</t>
         </is>
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>多格式导出</t>
+          <t>原材料库</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>export(PDF/Word/Excel)</t>
+          <t>view/create/edit/delete</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>支持 PDF/Word（含水印）/Excel（多Sheet）导出</t>
+          <t>CRUD 物料：品名/编码/规格/分类/供应商/单价，设置部门归属（私有/全局）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="22" t="inlineStr">
-        <is>
-          <t>全局</t>
-        </is>
-      </c>
-      <c r="B30" s="22" t="inlineStr">
-        <is>
-          <t>消息通知</t>
-        </is>
-      </c>
-      <c r="C30" s="22" t="inlineStr">
-        <is>
-          <t>view</t>
-        </is>
-      </c>
-      <c r="D30" s="22" t="inlineStr">
-        <is>
-          <t>查看站内消息：审批通知/变更通知/归档通知</t>
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>物料清单</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>批量导入</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>import/preview/confirm</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>Excel 批量导入，先预览确认后入库，按 code 精确匹配，存在则覆盖</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
+          <t>物料清单</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>分类系数</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>view/edit</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>配置大件/普通件/其他件系数，报价计算时自动应用（与销售部税率配置并列）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>物料清单</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>物料使用历史</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>查看物料被哪些报价单/项目使用过，便于成本参考和复用</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
           <t>全局</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>消息订阅</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>subscribe</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>用户配置订阅类型，减少噪音</t>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>版本快照</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>view/create</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>每次保存/提交/审批自动生成快照，存储完整报价结构，版本可追溯</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>版本对比</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>对比任意两个版本，字段级差异高亮展示（绿色=新增/红色=删除/橙色=修改）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>多格式导出</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>export(PDF/Word/Excel)</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>支持 PDF（已有）/Word（含水印、版本号、审核状态）/Excel（多Sheet）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>消息通知</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>查看站内消息：审批通知/变更通知/归档通知</t>
         </is>
       </c>
     </row>
@@ -1767,9 +1877,9 @@
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
@@ -1780,13 +1890,13 @@
     <col width="7" customWidth="1" min="11" max="11"/>
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="23" t="inlineStr">
         <is>
-          <t>分类</t>
+          <t>负责部门</t>
         </is>
       </c>
       <c r="B1" s="23" t="inlineStr">
@@ -1902,7 +2012,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="29" t="inlineStr">
         <is>
-          <t>机构部</t>
+          <t>销售部</t>
         </is>
       </c>
       <c r="B3" s="30" t="inlineStr">
@@ -1912,7 +2022,7 @@
       </c>
       <c r="C3" s="30" t="inlineStr">
         <is>
-          <t>第1周周四~第2周周二</t>
+          <t>第1周 周四~第2周 周二</t>
         </is>
       </c>
       <c r="D3" s="31" t="inlineStr">
@@ -1939,14 +2049,14 @@
       <c r="M3" s="27" t="inlineStr"/>
       <c r="N3" s="28" t="inlineStr">
         <is>
-          <t>机构信息/联系人/费用项/数据隔离</t>
+          <t>税率/系数/人力单价/运输单价/机票签证单价</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="32" t="inlineStr">
         <is>
-          <t>电控软件部</t>
+          <t>机构部</t>
         </is>
       </c>
       <c r="B4" s="33" t="inlineStr">
@@ -1956,7 +2066,7 @@
       </c>
       <c r="C4" s="33" t="inlineStr">
         <is>
-          <t>第2周 周三~周五</t>
+          <t>第2周 周三~第3周 周二</t>
         </is>
       </c>
       <c r="D4" s="27" t="inlineStr"/>
@@ -1983,14 +2093,14 @@
       <c r="M4" s="27" t="inlineStr"/>
       <c r="N4" s="28" t="inlineStr">
         <is>
-          <t>电控模块/BOM/工时记录/费用项</t>
+          <t>机构模块划分/BOM清单/机构专属物料/费用项</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
-          <t>项目部</t>
+          <t>电控软件部</t>
         </is>
       </c>
       <c r="B5" s="36" t="inlineStr">
@@ -2000,11 +2110,15 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>第3周 周一~周三</t>
+          <t>第2周 周三~第3周 周二</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr"/>
-      <c r="E5" s="27" t="inlineStr"/>
+      <c r="E5" s="37" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="F5" s="37" t="inlineStr">
         <is>
           <t>█</t>
@@ -2015,11 +2129,7 @@
           <t>█</t>
         </is>
       </c>
-      <c r="H5" s="37" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="H5" s="27" t="inlineStr"/>
       <c r="I5" s="27" t="inlineStr"/>
       <c r="J5" s="27" t="inlineStr"/>
       <c r="K5" s="27" t="inlineStr"/>
@@ -2027,14 +2137,14 @@
       <c r="M5" s="27" t="inlineStr"/>
       <c r="N5" s="28" t="inlineStr">
         <is>
-          <t>项目信息/成员权限/进度/文档</t>
+          <t>电控模块划分/BOM清单/电控专属物料/费用项</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="38" t="inlineStr">
         <is>
-          <t>销售部</t>
+          <t>项目部</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
@@ -2044,12 +2154,16 @@
       </c>
       <c r="C6" s="39" t="inlineStr">
         <is>
-          <t>第3周周四~第4周周二</t>
+          <t>第3周 周三~第4周 周二</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr"/>
       <c r="E6" s="27" t="inlineStr"/>
-      <c r="F6" s="27" t="inlineStr"/>
+      <c r="F6" s="40" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="G6" s="40" t="inlineStr">
         <is>
           <t>█</t>
@@ -2060,18 +2174,14 @@
           <t>█</t>
         </is>
       </c>
-      <c r="I6" s="40" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="I6" s="27" t="inlineStr"/>
       <c r="J6" s="27" t="inlineStr"/>
       <c r="K6" s="27" t="inlineStr"/>
       <c r="L6" s="27" t="inlineStr"/>
       <c r="M6" s="27" t="inlineStr"/>
       <c r="N6" s="28" t="inlineStr">
         <is>
-          <t>客户管理/报价发起/价格策略/统计</t>
+          <t>工时记录/工时审批/运输单元/差旅人次</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2204,11 @@
       <c r="D7" s="27" t="inlineStr"/>
       <c r="E7" s="27" t="inlineStr"/>
       <c r="F7" s="27" t="inlineStr"/>
-      <c r="G7" s="27" t="inlineStr"/>
+      <c r="G7" s="43" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
       <c r="H7" s="43" t="inlineStr">
         <is>
           <t>█</t>
@@ -2105,17 +2219,13 @@
           <t>█</t>
         </is>
       </c>
-      <c r="J7" s="43" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
+      <c r="J7" s="27" t="inlineStr"/>
       <c r="K7" s="27" t="inlineStr"/>
       <c r="L7" s="27" t="inlineStr"/>
       <c r="M7" s="27" t="inlineStr"/>
       <c r="N7" s="28" t="inlineStr">
         <is>
-          <t>原材料库/批量导入/分类系数/使用历史</t>
+          <t>原材料库/批量导入/部门归属/使用历史</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2325,7 @@
       </c>
       <c r="N9" s="28" t="inlineStr">
         <is>
-          <t>功能/权限/性能测试/回归/Bug修复/部署</t>
+          <t>功能/权限/性能测试/回归/部署验证</t>
         </is>
       </c>
     </row>

--- a/docs/V2.1开发计划_领导版.xlsx
+++ b/docs/V2.1开发计划_领导版.xlsx
@@ -78,7 +78,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -133,6 +133,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F1F8E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
     <fill>
@@ -210,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -251,7 +256,13 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -275,7 +286,7 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -290,7 +301,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -357,6 +368,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -724,14 +753,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="58" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -767,7 +796,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="102" customHeight="1">
+    <row r="2" ht="108" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -802,7 +831,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="102" customHeight="1">
+    <row r="3" ht="108" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -825,9 +854,9 @@
         <is>
           <t>• 税率配置：设置默认税率（0/3/6/13/17%），支持按客户/项目差异化配置
 • 物料分类系数：配置大件/普通件/其他件 分类系数，报价计算时自动应用
-• 人力费用单价：按工种（电控设计/软件开发/现场调试/装配）配置每小时单价（元/小时）
+• 人力费用单价：按工种（电控设计/软件开发/装配/调试/安装）配置每小时单价（元/小时），内部/外部分开
 • 运输费用单价：配置每次运输单元的单价（元/次），含国内/国外不同报价
-• 机票+签证费用单价：配置单人机票价（元/张）和单人签证费（元/人）
+• 机票+签证费用单价：配置单人机票价（元/张）和单人签证费（元/人），含国内/国外不同报价
 • 报价有效期配置：设置默认报价有效期天数，超期自动提醒
 • 费用参数历史：记录费用单价变更历史，版本可追溯</t>
         </is>
@@ -838,7 +867,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="102" customHeight="1">
+    <row r="4" ht="108" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -859,21 +888,20 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>• 机构模块划分：根据产品类型，将报价单划分为多个机构模块（结构设计/钣金件/标准件/外购件等）
+          <t>• 机构模块划分：根据产品类型，将报价单划分为多个机构模块（结构设计/钣金件/标准件/外购件等），支持拖拽排序
 • 机构 BOM 清单：从原材料库选择物料，填入各机构模块，支持批量添加
 • 机构专属物料：可录入仅本机构使用的私有物料（ department_id 隔离）
 • 模块参与人：设置业务负责人（business_lead）和查看者（viewer）
-• 机构费用项：模块级其他费用（调试费/培训费/证书费等），支持内部/外部不同计价
-• 机构模块权限：机构部用户只能编辑本部门的模块内容，view 权限按参与人分配</t>
+• 机构费用项：模块级其他费用（调试费/培训费/证书费等），支持内部/外部不同计价</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>机构部负责机械/结构类模块，是报价单物料的主要来源，需与电控软件部协同</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="102" customHeight="1">
+          <t>机构部负责机械/结构类模块，是报价单物料的主要来源，与电控软件部并行工作</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="108" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -894,12 +922,10 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>• 电控模块划分：根据产品类型，将报价单划分为多个电控/软件模块（PLC控制/变频器/触摸屏/软件组态等）
+          <t>• 电控模块划分：根据产品类型，将报价单划分为多个电控/软件模块（PLC控制/变频器/触摸屏/软件组态），支持拖拽排序
 • 电控 BOM 清单：从原材料库选择物料，填入各电控模块，支持批量添加
 • 电控专属物料：可录入仅本电控部使用的私有物料（ department_id 隔离）
-• 电控工种配置：配置电控设计/软件开发/现场调试各工种的小时费率
-• 电控费用项：模块级其他费用（电控设计费/PLC编程费/现场调试费等），支持内部/外部不同计价
-• 电控模块权限：电控软件部用户只能编辑本部门的模块内容</t>
+• 电控费用项：模块级其他费用（电控设计费/PLC编程费/现场调试费等），支持内部/外部不同计价</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -908,7 +934,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="102" customHeight="1">
+    <row r="6" ht="108" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -919,7 +945,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>3天</t>
+          <t>4天</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -929,21 +955,20 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>• 工时记录：按工种（电控设计/软件开发/装配/调试/安装）录入工时数量（小时），自动关联人力费用单价
-• 工时内容：记录每条工时的具体工作内容，便于追溯和审计
+          <t>• 工时记录：按工种（电控设计/软件开发/装配/调试/安装）录入工时数量（小时）和工作内容，关联人力费用单价，自动计算成本
 • 工时审批：项目负责人审批工时记录，确认后自动写入报价单 OtherFee（人力费用）
-• 运输单元配置：填写本次报价需要的运输次数（每次的运费单价由销售部配置）
-• 差旅人次配置：填写本次报价需要的机票数量和签证人数（单人单价由销售部配置）
-• 参与人权限：项目成员 view/edit 本项目报价单的工时/运输/差旅部分</t>
+• 运输单元配置：填写本次报价需要的运输次数，关联销售部配置的单价，自动计算运输费用
+• 差旅人次配置：填写本次报价需要的机票数量和签证人数，关联销售部配置的单价，自动计算差旅费用
+• 项目进度管理：维护项目阶段进度（方案/采购/生产/调试/验收），进度百分比展示</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>项目部填写的内容（工时×单价 + 运输次数 + 差旅人次）构成报价单的主要非物料成本</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="102" customHeight="1">
+          <t>项目部填写的内容（工时×单价 + 运输次数×单价 + 差旅人次×单价）构成报价单的主要非物料成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="108" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -978,7 +1003,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="102" customHeight="1">
+    <row r="8" ht="108" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -989,12 +1014,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>5天</t>
+          <t>6天</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>第5周 全周</t>
+          <t>第5周~第6周</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1005,49 +1030,115 @@
 • 版本快照增强：每次保存/提交/审批自动生成快照，存储完整报价结构 JSON
 • 版本对比 API：GET /versions/&lt;id&gt;/compare?v1=X&amp;v2=Y，返回物料/费用/金额字段级差异
 • 版本对比前端页：左右分栏展示，高亮差异字段（绿色=新增/红色=删除/橙色=修改）
-• 多格式导出：PDF（已有）/ Word（python-docx，含水印、版本号）/ Excel（openpyxl，多Sheet：封面+物料+费用汇总）</t>
+• 多格式导出：PDF（已有）/ Word（python-docx，含水印、版本号）/ Excel（openpyxl，多Sheet）</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>整合测试：销售参数是否正确引用、机构/电控 BOM 是否正确汇总、项目费用是否正确联动</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="102" customHeight="1">
+          <t>W5前半周完成流程串联+金额引擎，后半周完成版本对比+多格式导出</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="108" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
+          <t>缓冲打磨</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>3天</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>第7周 全周</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>• 跨部门数据流联调：验证机构 BOM+电控 BOM+项目工时费用是否正确汇总到报价单总价
+• 费用联动验证：修改税率/工时数/运输次数后，报价单汇总金额是否实时正确更新
+• 权限链路验证：各部门用户只能编辑/查看本部门数据，admin 全局访问
+• UI 细节打磨：按钮状态统一 / 错误提示 / 表单必填校验 / 空状态页面 / 表格性能优化
+• 性能优化：100+ 物料报价单加载 &lt; 2秒，批量导入 500 行 &lt; 10 秒</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>预留缓冲，应对联调过程中发现的边界问题和细节问题</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="108" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
           <t>测试部署</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>4天</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>第6周 全周</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>5天</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>第8周~第9周</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>• 功能测试：报价单完整生命周期（创建→各部门填写→汇总→审批→归档）
 • 权限测试：跨部门数据隔离 / 角色权限矩阵 / admin 全局权限 / 参与人权限
-• 费用联动测试：修改工时数量→报价单汇总金额自动更新；修改税率→税额自动重算
-• 性能测试：100+ 物料报价单加载 &lt; 2秒 / 批量导入 500 行 &lt; 10 秒
 • 数据库索引优化：quotations.department_id / modules.quotation_id / operation_logs.created_at
 • 回归测试：全量 API Postman 批量用例，核心路径 100% 通过
-• Bug 修复 + 细节打磨：按钮状态 / 错误提示 / 表单校验 / 空状态页面
+• Bug 修复：按钮状态 / 错误提示 / 表单校验 / 空状态页面
+• 备份恢复验证：pg_dump 全量备份 + 模拟数据恢复测试
 • Docker Swarm 重新构建镜像 + 生产环境部署 + 冒烟测试</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>预留 2 天缓冲（第 7~8 周），应对突发问题</t>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>W8 全周测试 + W9 周一~周三 部署，W9 周四~周五 预留</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="108" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>缓冲上线</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>2天</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>第10周 周一~周二</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>• 生产环境验证：最终冒烟测试，核心路径全通过后宣布 V2.1 上线
+• 文档更新：用户操作手册（协助测试组完成）
+• 数据备份：上线前全量备份，保留回滚方案
+• 预留突发问题处理：如有问题立即回滚，上线后 48 小时值班监控</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>W10 周三起正式进入运维阶段，V2.1 上线完成</t>
         </is>
       </c>
     </row>
@@ -1066,798 +1157,798 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>所属部门</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>职责模块</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>权限动作</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>详细说明</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>系统管理</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>部门管理</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>新增/编辑/删除部门，设置部门经理，维护部门层级关系</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>系统管理</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>用户管理</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>创建/编辑/冻结用户，分配部门，设置跨部门权限标记（is_cross_dept）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>系统管理</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>角色权限</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>配置角色权限矩阵（view/create/edit/delete/approve），支持部门级管理员</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>系统管理</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>权限中间件</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>create/edit/delete</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>API 层面自动过滤 department_id，普通用户仅访问本部门数据</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>系统管理</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>操作日志</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>view</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>查看所有用户的关键操作记录（谁/何时/对什么/做了什么）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>销售部</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>税率配置</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>view/edit</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>设置默认税率（0/3/6/13/17%），支持按客户/项目差异化配置，版本可追溯</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>销售部</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>物料分类系数</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>view/edit</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>配置大件/普通件/其他件 分类系数，报价计算时自动应用</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>销售部</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>人力费用单价</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>view/edit</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>按工种（电控设计/软件开发/装配/调试/安装）配置每小时单价（元/小时），内部/外部分开</t>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>按工种（电控设计/软件开发/装配/调试/安装）配置每小时单价（元/小时），内部/外部分开报价</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>销售部</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>运输费用单价</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>view/edit</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>配置每次运输单元的单价（元/次），含国内/国外不同报价标准</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>销售部</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>机票+签证单价</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>view/edit</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>配置单人机票价（元/张）和单人签证费（元/人），含国内/国外不同报价标准</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>销售部</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>报价有效期配置</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>view/edit</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>设置默认报价有效期天数，超期自动提醒</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>销售部</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>销售统计</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>view</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>按销售负责人统计报价单数量、总额、成交率、丢单原因分析</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>销售部</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>报价单发起</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>create/submit</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>发起新报价单，自动带销售部门标记，追踪报价单全流程状态</t>
         </is>
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>机构部</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>机构模块划分</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>create/edit/delete</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>将报价单划分为多个机构模块（结构设计/钣金件/标准件/外购件），拖拽排序</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>机构部</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>机构 BOM 清单</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>从原材料库选择物料填入各机构模块，支持批量添加/删除/编辑数量</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>机构部</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>机构专属物料</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>录入仅本机构使用的私有物料，department_id 隔离，其他部门不可见</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>机构部</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>模块参与人</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>view/create/edit</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>设置模块业务负责人（business_lead）和查看者（viewer）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>机构部</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>机构费用项</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>模块级其他费用（调试费/培训费/证书费等），支持内部/外部不同计价</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>电控软件部</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>电控模块划分</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>create/edit/delete</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>将报价单划分为多个电控/软件模块（PLC控制/变频器/触摸屏/软件组态），拖拽排序</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>电控软件部</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>电控 BOM 清单</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>从原材料库选择物料填入各电控模块，支持批量添加/删除/编辑数量</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>电控软件部</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>电控专属物料</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>录入仅本电控部使用的私有物料，department_id 隔离，其他部门不可见</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>电控软件部</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>电控费用项</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>模块级其他费用（电控设计费/PLC编程费/现场调试费），支持内部/外部不同计价</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>项目部</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>工时记录</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>按工种录入工时数量（小时）和工作内容，关联人力费用单价，自动计算成本</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>项目部</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>工时审批</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>approve/reject</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>项目负责人审批工时记录，确认后自动写入报价单 OtherFee（人力费用）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>项目部</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>运输单元</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>填写本次报价需要的运输次数，关联销售部配置的单价，自动计算运输费用</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>项目部</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>差旅人次</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="18" t="inlineStr">
         <is>
           <t>填写本次报价需要的机票数量和签证人数，关联销售部配置的单价，自动计算差旅费用</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>项目部</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>项目进度</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>view/edit</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>维护项目阶段进度（方案/采购/生产/调试/验收），进度百分比展示</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>物料清单</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>原材料库</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C29" s="18" t="inlineStr">
         <is>
           <t>view/create/edit/delete</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>CRUD 物料：品名/编码/规格/分类/供应商/单价，设置部门归属（私有/全局）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>物料清单</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>批量导入</t>
         </is>
       </c>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>import/preview/confirm</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>Excel 批量导入，先预览确认后入库，按 code 精确匹配，存在则覆盖</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>物料清单</t>
         </is>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>分类系数</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>view/edit</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>配置大件/普通件/其他件系数，报价计算时自动应用（与销售部税率配置并列）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>物料清单</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>物料使用历史</t>
         </is>
       </c>
-      <c r="C32" s="21" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>view</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>查看物料被哪些报价单/项目使用过，便于成本参考和复用</t>
         </is>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>全局</t>
         </is>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="18" t="inlineStr">
         <is>
           <t>版本快照</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C33" s="18" t="inlineStr">
         <is>
           <t>view/create</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>每次保存/提交/审批自动生成快照，存储完整报价结构，版本可追溯</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>全局</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>版本对比</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>view</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="24" t="inlineStr">
         <is>
           <t>对比任意两个版本，字段级差异高亮展示（绿色=新增/红色=删除/橙色=修改）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>全局</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>多格式导出</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C35" s="18" t="inlineStr">
         <is>
           <t>export(PDF/Word/Excel)</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>支持 PDF（已有）/Word（含水印、版本号、审核状态）/Excel（多Sheet）</t>
+      <c r="D35" s="18" t="inlineStr">
+        <is>
+          <t>支持 PDF（已有）/Word（含水印、版本号、审核状态）/Excel（多Sheet：封面+物料+费用汇总）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="A36" s="24" t="inlineStr">
         <is>
           <t>全局</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="24" t="inlineStr">
         <is>
           <t>消息通知</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>view</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>查看站内消息：审批通知/变更通知/归档通知</t>
         </is>
@@ -1874,7 +1965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1894,438 +1985,498 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>负责部门</t>
         </is>
       </c>
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>时长</t>
         </is>
       </c>
-      <c r="C1" s="23" t="inlineStr">
+      <c r="C1" s="25" t="inlineStr">
         <is>
           <t>时间段</t>
         </is>
       </c>
-      <c r="D1" s="23" t="inlineStr">
+      <c r="D1" s="25" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E1" s="25" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="F1" s="23" t="inlineStr">
+      <c r="F1" s="25" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="G1" s="23" t="inlineStr">
+      <c r="G1" s="25" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="H1" s="23" t="inlineStr">
+      <c r="H1" s="25" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="I1" s="23" t="inlineStr">
+      <c r="I1" s="25" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="J1" s="23" t="inlineStr">
+      <c r="J1" s="25" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="K1" s="23" t="inlineStr">
+      <c r="K1" s="25" t="inlineStr">
         <is>
           <t>W8</t>
         </is>
       </c>
-      <c r="L1" s="23" t="inlineStr">
+      <c r="L1" s="25" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="M1" s="23" t="inlineStr">
+      <c r="M1" s="25" t="inlineStr">
         <is>
           <t>W10</t>
         </is>
       </c>
-      <c r="N1" s="23" t="inlineStr">
+      <c r="N1" s="25" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>系统管理</t>
         </is>
       </c>
-      <c r="B2" s="25" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>3天</t>
         </is>
       </c>
-      <c r="C2" s="25" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>第1周 周一~周三</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="E2" s="26" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="F2" s="26" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="G2" s="27" t="inlineStr"/>
-      <c r="H2" s="27" t="inlineStr"/>
-      <c r="I2" s="27" t="inlineStr"/>
-      <c r="J2" s="27" t="inlineStr"/>
-      <c r="K2" s="27" t="inlineStr"/>
-      <c r="L2" s="27" t="inlineStr"/>
-      <c r="M2" s="27" t="inlineStr"/>
-      <c r="N2" s="28" t="inlineStr">
+      <c r="D2" s="28" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="E2" s="28" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="F2" s="28" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="G2" s="29" t="inlineStr"/>
+      <c r="H2" s="29" t="inlineStr"/>
+      <c r="I2" s="29" t="inlineStr"/>
+      <c r="J2" s="29" t="inlineStr"/>
+      <c r="K2" s="29" t="inlineStr"/>
+      <c r="L2" s="29" t="inlineStr"/>
+      <c r="M2" s="29" t="inlineStr"/>
+      <c r="N2" s="30" t="inlineStr">
         <is>
           <t>部门/用户/角色/权限中间件，数据迁移</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>销售部</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>3天</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>第1周 周四~第2周 周二</t>
         </is>
       </c>
-      <c r="D3" s="31" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="E3" s="31" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="F3" s="31" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="G3" s="27" t="inlineStr"/>
-      <c r="H3" s="27" t="inlineStr"/>
-      <c r="I3" s="27" t="inlineStr"/>
-      <c r="J3" s="27" t="inlineStr"/>
-      <c r="K3" s="27" t="inlineStr"/>
-      <c r="L3" s="27" t="inlineStr"/>
-      <c r="M3" s="27" t="inlineStr"/>
-      <c r="N3" s="28" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr"/>
+      <c r="E3" s="33" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="F3" s="33" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="G3" s="33" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="H3" s="29" t="inlineStr"/>
+      <c r="I3" s="29" t="inlineStr"/>
+      <c r="J3" s="29" t="inlineStr"/>
+      <c r="K3" s="29" t="inlineStr"/>
+      <c r="L3" s="29" t="inlineStr"/>
+      <c r="M3" s="29" t="inlineStr"/>
+      <c r="N3" s="30" t="inlineStr">
         <is>
           <t>税率/系数/人力单价/运输单价/机票签证单价</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>机构部</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>3天</t>
         </is>
       </c>
-      <c r="C4" s="33" t="inlineStr">
+      <c r="C4" s="35" t="inlineStr">
         <is>
           <t>第2周 周三~第3周 周二</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr"/>
-      <c r="E4" s="34" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="F4" s="34" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="G4" s="34" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="H4" s="27" t="inlineStr"/>
-      <c r="I4" s="27" t="inlineStr"/>
-      <c r="J4" s="27" t="inlineStr"/>
-      <c r="K4" s="27" t="inlineStr"/>
-      <c r="L4" s="27" t="inlineStr"/>
-      <c r="M4" s="27" t="inlineStr"/>
-      <c r="N4" s="28" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr"/>
+      <c r="E4" s="36" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="F4" s="36" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="G4" s="36" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="H4" s="29" t="inlineStr"/>
+      <c r="I4" s="29" t="inlineStr"/>
+      <c r="J4" s="29" t="inlineStr"/>
+      <c r="K4" s="29" t="inlineStr"/>
+      <c r="L4" s="29" t="inlineStr"/>
+      <c r="M4" s="29" t="inlineStr"/>
+      <c r="N4" s="30" t="inlineStr">
         <is>
           <t>机构模块划分/BOM清单/机构专属物料/费用项</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>电控软件部</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>3天</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>第2周 周三~第3周 周二</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr"/>
-      <c r="E5" s="37" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="F5" s="37" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="G5" s="37" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="H5" s="27" t="inlineStr"/>
-      <c r="I5" s="27" t="inlineStr"/>
-      <c r="J5" s="27" t="inlineStr"/>
-      <c r="K5" s="27" t="inlineStr"/>
-      <c r="L5" s="27" t="inlineStr"/>
-      <c r="M5" s="27" t="inlineStr"/>
-      <c r="N5" s="28" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr"/>
+      <c r="E5" s="39" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="F5" s="39" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="G5" s="39" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="H5" s="29" t="inlineStr"/>
+      <c r="I5" s="29" t="inlineStr"/>
+      <c r="J5" s="29" t="inlineStr"/>
+      <c r="K5" s="29" t="inlineStr"/>
+      <c r="L5" s="29" t="inlineStr"/>
+      <c r="M5" s="29" t="inlineStr"/>
+      <c r="N5" s="30" t="inlineStr">
         <is>
           <t>电控模块划分/BOM清单/电控专属物料/费用项</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>项目部</t>
         </is>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>4天</t>
+        </is>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>第3周 周三~第4周 周二</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="inlineStr"/>
+      <c r="E6" s="29" t="inlineStr"/>
+      <c r="F6" s="42" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="G6" s="42" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="H6" s="42" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="I6" s="29" t="inlineStr"/>
+      <c r="J6" s="29" t="inlineStr"/>
+      <c r="K6" s="29" t="inlineStr"/>
+      <c r="L6" s="29" t="inlineStr"/>
+      <c r="M6" s="29" t="inlineStr"/>
+      <c r="N6" s="30" t="inlineStr">
+        <is>
+          <t>工时记录/工时审批/运输单元/差旅人次</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>物料清单</t>
+        </is>
+      </c>
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>3天</t>
         </is>
       </c>
-      <c r="C6" s="39" t="inlineStr">
-        <is>
-          <t>第3周 周三~第4周 周二</t>
-        </is>
-      </c>
-      <c r="D6" s="27" t="inlineStr"/>
-      <c r="E6" s="27" t="inlineStr"/>
-      <c r="F6" s="40" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="G6" s="40" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="H6" s="40" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="I6" s="27" t="inlineStr"/>
-      <c r="J6" s="27" t="inlineStr"/>
-      <c r="K6" s="27" t="inlineStr"/>
-      <c r="L6" s="27" t="inlineStr"/>
-      <c r="M6" s="27" t="inlineStr"/>
-      <c r="N6" s="28" t="inlineStr">
-        <is>
-          <t>工时记录/工时审批/运输单元/差旅人次</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="41" t="inlineStr">
-        <is>
-          <t>物料清单</t>
-        </is>
-      </c>
-      <c r="B7" s="42" t="inlineStr">
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t>第4周 周三~周五</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr"/>
+      <c r="E7" s="29" t="inlineStr"/>
+      <c r="F7" s="29" t="inlineStr"/>
+      <c r="G7" s="45" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="H7" s="45" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="I7" s="45" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="J7" s="29" t="inlineStr"/>
+      <c r="K7" s="29" t="inlineStr"/>
+      <c r="L7" s="29" t="inlineStr"/>
+      <c r="M7" s="29" t="inlineStr"/>
+      <c r="N7" s="30" t="inlineStr">
+        <is>
+          <t>原材料库/批量导入/部门归属/使用历史</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="46" t="inlineStr">
+        <is>
+          <t>整合模块功能</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>6天</t>
+        </is>
+      </c>
+      <c r="C8" s="47" t="inlineStr">
+        <is>
+          <t>第5周~第6周</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr"/>
+      <c r="E8" s="29" t="inlineStr"/>
+      <c r="F8" s="29" t="inlineStr"/>
+      <c r="G8" s="29" t="inlineStr"/>
+      <c r="H8" s="29" t="inlineStr"/>
+      <c r="I8" s="48" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="J8" s="48" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="K8" s="48" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="L8" s="48" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="M8" s="29" t="inlineStr"/>
+      <c r="N8" s="30" t="inlineStr">
+        <is>
+          <t>流程串联/金额引擎/版本对比/多格式导出</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="49" t="inlineStr">
+        <is>
+          <t>缓冲打磨</t>
+        </is>
+      </c>
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>3天</t>
         </is>
       </c>
-      <c r="C7" s="42" t="inlineStr">
-        <is>
-          <t>第4周 周三~周五</t>
-        </is>
-      </c>
-      <c r="D7" s="27" t="inlineStr"/>
-      <c r="E7" s="27" t="inlineStr"/>
-      <c r="F7" s="27" t="inlineStr"/>
-      <c r="G7" s="43" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="H7" s="43" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="I7" s="43" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="J7" s="27" t="inlineStr"/>
-      <c r="K7" s="27" t="inlineStr"/>
-      <c r="L7" s="27" t="inlineStr"/>
-      <c r="M7" s="27" t="inlineStr"/>
-      <c r="N7" s="28" t="inlineStr">
-        <is>
-          <t>原材料库/批量导入/部门归属/使用历史</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="44" t="inlineStr">
-        <is>
-          <t>整合模块功能</t>
-        </is>
-      </c>
-      <c r="B8" s="45" t="inlineStr">
+      <c r="C9" s="50" t="inlineStr">
+        <is>
+          <t>第7周 全周</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr"/>
+      <c r="E9" s="29" t="inlineStr"/>
+      <c r="F9" s="29" t="inlineStr"/>
+      <c r="G9" s="29" t="inlineStr"/>
+      <c r="H9" s="29" t="inlineStr"/>
+      <c r="I9" s="29" t="inlineStr"/>
+      <c r="J9" s="29" t="inlineStr"/>
+      <c r="K9" s="51" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="L9" s="29" t="inlineStr"/>
+      <c r="M9" s="29" t="inlineStr"/>
+      <c r="N9" s="30" t="inlineStr">
+        <is>
+          <t>联调/权限验证/UI打磨/性能优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="52" t="inlineStr">
+        <is>
+          <t>测试部署</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t>5天</t>
         </is>
       </c>
-      <c r="C8" s="45" t="inlineStr">
-        <is>
-          <t>第5周 全周</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr"/>
-      <c r="E8" s="27" t="inlineStr"/>
-      <c r="F8" s="27" t="inlineStr"/>
-      <c r="G8" s="27" t="inlineStr"/>
-      <c r="H8" s="27" t="inlineStr"/>
-      <c r="I8" s="46" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="J8" s="46" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="K8" s="46" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="L8" s="46" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="M8" s="46" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="N8" s="28" t="inlineStr">
-        <is>
-          <t>流程串联/金额引擎/版本对比/多格式导出</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="47" t="inlineStr">
-        <is>
-          <t>测试部署</t>
-        </is>
-      </c>
-      <c r="B9" s="48" t="inlineStr">
-        <is>
-          <t>4天</t>
-        </is>
-      </c>
-      <c r="C9" s="48" t="inlineStr">
-        <is>
-          <t>第6周 全周</t>
-        </is>
-      </c>
-      <c r="D9" s="27" t="inlineStr"/>
-      <c r="E9" s="27" t="inlineStr"/>
-      <c r="F9" s="27" t="inlineStr"/>
-      <c r="G9" s="27" t="inlineStr"/>
-      <c r="H9" s="27" t="inlineStr"/>
-      <c r="I9" s="27" t="inlineStr"/>
-      <c r="J9" s="49" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="K9" s="49" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="L9" s="49" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="M9" s="49" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="N9" s="28" t="inlineStr">
+      <c r="C10" s="53" t="inlineStr">
+        <is>
+          <t>第8周~第9周</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr"/>
+      <c r="E10" s="29" t="inlineStr"/>
+      <c r="F10" s="29" t="inlineStr"/>
+      <c r="G10" s="29" t="inlineStr"/>
+      <c r="H10" s="29" t="inlineStr"/>
+      <c r="I10" s="29" t="inlineStr"/>
+      <c r="J10" s="29" t="inlineStr"/>
+      <c r="K10" s="29" t="inlineStr"/>
+      <c r="L10" s="54" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="M10" s="54" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="N10" s="30" t="inlineStr">
         <is>
           <t>功能/权限/性能测试/回归/部署验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="55" t="inlineStr">
+        <is>
+          <t>缓冲上线</t>
+        </is>
+      </c>
+      <c r="B11" s="56" t="inlineStr">
+        <is>
+          <t>2天</t>
+        </is>
+      </c>
+      <c r="C11" s="56" t="inlineStr">
+        <is>
+          <t>第10周 周一~周二</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr"/>
+      <c r="E11" s="29" t="inlineStr"/>
+      <c r="F11" s="29" t="inlineStr"/>
+      <c r="G11" s="29" t="inlineStr"/>
+      <c r="H11" s="29" t="inlineStr"/>
+      <c r="I11" s="29" t="inlineStr"/>
+      <c r="J11" s="29" t="inlineStr"/>
+      <c r="K11" s="29" t="inlineStr"/>
+      <c r="L11" s="29" t="inlineStr"/>
+      <c r="M11" s="57" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="N11" s="30" t="inlineStr">
+        <is>
+          <t>生产冒烟/文档/备份/预留突发问题</t>
         </is>
       </c>
     </row>
